--- a/data/production/production_2026-W41.xlsx
+++ b/data/production/production_2026-W41.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -488,26 +488,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HO-238948</t>
+          <t>AU-694253</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Samuel Brennan</t>
+          <t>Victor Castillo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2773.51</v>
+        <v>1867.4</v>
       </c>
     </row>
     <row r="5">
@@ -516,22 +516,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LF-874415</t>
+          <t>AU-741188</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ivy Okafor</t>
+          <t>Mila Tanaka</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1310.79</v>
+        <v>2413.12</v>
       </c>
     </row>
     <row r="6">
@@ -549,22 +549,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AU-944554</t>
+          <t>AU-338805</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Clara Haines</t>
+          <t>Jonah Quill</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t xml:space="preserve">Auto </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -572,10 +572,8 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>$2,048.21</t>
-        </is>
+      <c r="G6" t="n">
+        <v>1544.08</v>
       </c>
     </row>
     <row r="7">
@@ -584,22 +582,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luis Ortega </t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CM-722615</t>
+          <t>AU-452155</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>James Moreau</t>
+          <t>Caleb Whitfield</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -608,7 +606,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>6240.31</v>
+        <v>1368.94</v>
       </c>
     </row>
     <row r="8">
@@ -617,22 +615,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HO-789558</t>
+          <t>AU-541302</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>James Moreau</t>
+          <t>Isaac Holloway</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -641,31 +639,31 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1452.85</v>
+        <v>1068.86</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LF-606545</t>
+          <t>AU-683433</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nora Ashby</t>
+          <t>Samuel Ruiz</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t xml:space="preserve"> Auto</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -673,65 +671,67 @@
           <t>New</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>1761.58</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>$1,499.82</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AU-296653</t>
+          <t>LF-770641</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Grace Albright</t>
+          <t>Clara Pryor</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1993.97</v>
+        <v>1092.36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HO-211486</t>
+          <t>CM-284844</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Leah Okafor</t>
+          <t>Nora Ruiz</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -739,45 +739,41 @@
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>$1,875.03</t>
-        </is>
+      <c r="G11" t="n">
+        <v>5872.41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AU-856320</t>
+          <t>HO-905219</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Maria Moreau</t>
+          <t>Ruby Sorensen</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">New </t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>$1,379.38</t>
-        </is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2151.09</v>
       </c>
     </row>
     <row r="13">
@@ -786,31 +782,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CM-815338</t>
+          <t>LF-537189</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Clara Haines</t>
+          <t>Sofia Pryor</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>9724.15</v>
+        <v>1301.8</v>
       </c>
     </row>
     <row r="14">
@@ -819,31 +815,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priya Raman </t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LF-916779</t>
+          <t>AU-128414</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Theo Moreau</t>
+          <t>Maria Ashby</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Renewal</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>872.13</v>
+        <v>1740.36</v>
       </c>
     </row>
     <row r="15">
@@ -852,17 +848,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AU-574012</t>
+          <t>AU-126763</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Jonah Calloway</t>
+          <t>Caleb Whitfield</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -872,11 +868,11 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1070.11</v>
+        <v>1162.41</v>
       </c>
     </row>
     <row r="16">
@@ -885,22 +881,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LF-337256</t>
+          <t>AU-978203</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sofia Pryor</t>
+          <t>Ivy Hartley</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -909,31 +905,31 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1790.71</v>
+        <v>1027.71</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AU-952679</t>
+          <t>HO-805785</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hannah Haines</t>
+          <t>Zoe Marsh</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -942,61 +938,59 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>951.64</v>
+        <v>2265.89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Grant Fowler</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CM-213000</t>
+          <t>LF-319777</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Leah Okafor</t>
+          <t>Victor Petrov</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>$3,738.76</t>
-        </is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1137.19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luis Ortega </t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AU-771712</t>
+          <t>AU-549624</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Maria Ashby</t>
+          <t>Maria Moreau</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1010,40 +1004,40 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2410.02</v>
+        <v>2035.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CM-737894</t>
+          <t>AU-821579</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Owen Petrov</t>
+          <t>Nora Ruiz</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commercial </t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4017.07</v>
+        <v>1309.69</v>
       </c>
     </row>
     <row r="21">
@@ -1052,67 +1046,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CM-819656</t>
+          <t>AU-352176</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Marcus Ibsen</t>
+          <t>Owen Kowal</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>7763.05</v>
+        <v>1643.71</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46302</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Priya Raman</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>HO-540897</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Mila Tanaka</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>$1,568.99</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1120,31 +1082,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HO-947609</t>
+          <t>LF-498308</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Theo Moreau</t>
+          <t>Sofia Marsh</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t xml:space="preserve">New </t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1818.81</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="24">
@@ -1153,22 +1115,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HO-501936</t>
+          <t>LF-549519</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ivy Okafor</t>
+          <t>Felix Tanaka</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1177,92 +1139,92 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3283.76</v>
+        <v>628.53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>aisha bello</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AU-938754</t>
+          <t>AU-398931</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Leah Okafor</t>
+          <t>Clara Pryor</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auto </t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1478.57</v>
+        <v>1462.12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Luis Ortega</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LF-954551</t>
+          <t>HO-608100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Grace Albright</t>
+          <t>Alma Ashby</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>766.5700000000001</v>
+        <v>2370.34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>MAYA CHEN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AU-416822</t>
+          <t>AU-394185</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Hugo Kowal</t>
+          <t>Samuel Ruiz</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1272,35 +1234,35 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RENEWAL</t>
+          <t>New</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1342.24</v>
+        <v>932.3099999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Maya Chen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LF-900660</t>
+          <t>HO-703422</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Owen Petrov</t>
+          <t>Sofia Marsh</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1309,99 +1271,99 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1514</v>
+        <v>2643.67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LF-278795</t>
+          <t>HO-206504</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Clara Pryor</t>
+          <t>Ivy Okafor</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Life </t>
+          <t>Home</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>$2,054.18</t>
-        </is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1991.97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CM-810614</t>
+          <t>AU-777191</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Maria Moreau</t>
+          <t>Owen Kowal</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>renewal</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>7162.36</v>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>$2,357.91</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HO-398916</t>
+          <t>LF-103301</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Olivia Hartley</t>
+          <t>Maria Novak</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t xml:space="preserve"> Life</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1409,124 +1371,420 @@
           <t>Renewal</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>$2,489.16</t>
-        </is>
+      <c r="G31" t="n">
+        <v>1219.91</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AU-750803</t>
+          <t>LF-776874</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Adrian Okafor</t>
+          <t>Olivia Delgado</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>$1,851.60</t>
-        </is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1985.94</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HO-507135</t>
+          <t>LF-132064</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Maria Ashby</t>
+          <t>Ivy Okafor</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>2092.69</v>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>$700.01</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Aisha Bello</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>LF-439087</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Leah Okafor</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Life</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>2026.09</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Grant Fowler</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AU-354322</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Maria Ashby</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1080.35</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Luis Ortega</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AU-676085</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Grace Delgado</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1532.33</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Luis Ortega</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AU-983981</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Jonah Quill</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>2247.99</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Tom Becker</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>LF-427672</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Maria Novak</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>life</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>788.72</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tom Becker</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>LF-457971</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Grace Delgado</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Life</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1129.39</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
         <v>46304</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Tom Becker</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>LF-299834</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Maria Moreau</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Life</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Grant Fowler</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HO-774944</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Samuel Ruiz</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>$2,038.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" t="inlineStr">
+      <c r="G40" t="n">
+        <v>2610.65</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Luis Ortega</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AU-696400</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Ruby Ferreira</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>2026.86</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Maya Chen</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HO-213161</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Grace Albright</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1407.79</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Maya Chen</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>LF-746334</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Nora Ruiz</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1134.02</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>82634.21000000001</v>
+      <c r="G45" t="n">
+        <v>66550.97</v>
       </c>
     </row>
   </sheetData>
@@ -1540,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1578,16 +1836,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HO-398916</t>
+          <t>AU-452155</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2546.59</v>
+        <v>1378.16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1603,16 +1861,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CM-810614</t>
+          <t>AU-541302</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6707.97</v>
+        <v>958.95</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1628,16 +1886,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CM-815338</t>
+          <t>HO-213161</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8786.4</v>
+        <v>1378.96</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1653,16 +1911,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CM-737894</t>
+          <t>HO-703422</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3954.51</v>
+        <v>2528.91</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1678,7 +1936,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AU-416822</t>
+          <t>AU-741188</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1687,7 +1945,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1227.31</v>
+        <v>2364.13</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1703,7 +1961,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AU-794530</t>
+          <t>AU-696400</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1712,32 +1970,32 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1667.27</v>
+        <v>2044.01</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lost</t>
+          <t>Renewed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CM-722615</t>
+          <t>HO-805785</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6149.47</v>
+        <v>2213.06</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1748,21 +2006,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Luis Ortega</t>
+          <t>Priya Raman</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AU-771712</t>
+          <t>LF-319777</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2382.54</v>
+        <v>1159.53</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1778,16 +2036,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HO-507135</t>
+          <t>CM-284844</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1978.99</v>
+        <v>5633.62</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1803,7 +2061,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CM-819656</t>
+          <t>CM-957850</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1812,32 +2070,32 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7136.9</v>
+        <v>7017.25</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Renewed</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HO-789558</t>
+          <t>AU-549624</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1456.97</v>
+        <v>1937.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1848,21 +2106,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Tom Becker</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HO-947609</t>
+          <t>LF-776874</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1643.17</v>
+        <v>1989.72</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1878,16 +2136,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AU-574012</t>
+          <t>LF-103301</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>987.02</v>
+        <v>1216.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1903,41 +2161,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LF-900660</t>
+          <t>AU-897872</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1530.2</v>
+        <v>1274.72</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Renewed</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HO-501936</t>
+          <t>LF-549519</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Life</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3127.19</v>
+        <v>624.03</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1953,7 +2211,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AU-952679</t>
+          <t>AU-694253</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1962,7 +2220,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>975.12</v>
+        <v>1692.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1978,7 +2236,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LF-874415</t>
+          <t>LF-931858</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1987,109 +2245,59 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1194.14</v>
+        <v>1101.66</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Renewed</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LF-278795</t>
+          <t>AU-391954</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1860.37</v>
+        <v>2052.25</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Renewed</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Grant Fowler</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LF-954551</t>
+          <t>AU-128414</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Life</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>776.61</v>
+        <v>1739.41</v>
       </c>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>Renewed</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Grant Fowler</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>HO-211486</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1885.17</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Renewed</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Grant Fowler</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>AU-296653</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1816.28</v>
-      </c>
-      <c r="E22" t="inlineStr">
         <is>
           <t>Renewed</t>
         </is>
